--- a/data/raw/sales/Week 26/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 26/Audio_Array/other_channels.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 26\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DADE3E-7402-4845-AD21-857070DDF349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E617BE-DAFC-4FD9-BEB2-2B0C6118F449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
     <sheet name="Blinkit Sales" sheetId="8" r:id="rId2"/>
     <sheet name="B2B" sheetId="12" r:id="rId3"/>
+    <sheet name="Flipkart" sheetId="13" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">B2B!$A$1:$H$1</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="198">
   <si>
     <t>SKU</t>
   </si>
@@ -403,13 +404,241 @@
   </si>
   <si>
     <t>AH-60-BL</t>
+  </si>
+  <si>
+    <t>FBA79444</t>
+  </si>
+  <si>
+    <t>FBA75688</t>
+  </si>
+  <si>
+    <t>FBA79008</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>FBA76863</t>
+  </si>
+  <si>
+    <t>FBA79010</t>
+  </si>
+  <si>
+    <t>FBA75676</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>FBA77171</t>
+  </si>
+  <si>
+    <t>FBA75683</t>
+  </si>
+  <si>
+    <t>FBA79448</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>FBA75690</t>
+  </si>
+  <si>
+    <t>FBA75684</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>FBA79445</t>
+  </si>
+  <si>
+    <t>FBA78925</t>
+  </si>
+  <si>
+    <t>FBA79447</t>
+  </si>
+  <si>
+    <t>FBA75678</t>
+  </si>
+  <si>
+    <t>FBA75677</t>
+  </si>
+  <si>
+    <t>FBA75679</t>
+  </si>
+  <si>
+    <t>FBA78974</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>FBA79105</t>
+  </si>
+  <si>
+    <t>FBA79064</t>
+  </si>
+  <si>
+    <t>FBA78203</t>
+  </si>
+  <si>
+    <t>FBA76730</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>FBA75691</t>
+  </si>
+  <si>
+    <t>FBA79230</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>FBA78975</t>
+  </si>
+  <si>
+    <t>FBA78424</t>
+  </si>
+  <si>
+    <t>FBA75681</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>AM-W20</t>
+  </si>
+  <si>
+    <t>AM-W12</t>
+  </si>
+  <si>
+    <t>AI-06</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>AI-03</t>
+  </si>
+  <si>
+    <t>AM-C42</t>
+  </si>
+  <si>
+    <t>AM-C4</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>AC-6XL</t>
+  </si>
+  <si>
+    <t>AA-03</t>
+  </si>
+  <si>
+    <t>AM-W35</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>AA-04</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>AM-C11X</t>
+  </si>
+  <si>
+    <t>AM-W34</t>
+  </si>
+  <si>
+    <t>AA-01</t>
+  </si>
+  <si>
+    <t>AM-C5</t>
+  </si>
+  <si>
+    <t>AA-02</t>
+  </si>
+  <si>
+    <t>AA-20</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>AA-25</t>
+  </si>
+  <si>
+    <t>AM-C30</t>
+  </si>
+  <si>
+    <t>AM-C27</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>AM-W14</t>
+  </si>
+  <si>
+    <t>AM-W46</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>AA-21</t>
+  </si>
+  <si>
+    <t>AM-C37</t>
+  </si>
+  <si>
+    <t>AM-C7</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +685,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -489,7 +724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -512,11 +747,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -559,6 +809,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3686,4 +3945,1000 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D8AEDF-803D-4B23-865B-4867EBDC0DFD}">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="18">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>56809.322033898308</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="18">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>11790.677966101695</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="18">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>11263.5593220339</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="18">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>8538.9830508474588</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="18">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>8243.220338983052</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="18">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>6708.4745762711864</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3421.1864406779664</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>3228.8135593220341</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="18">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2849.1525423728817</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="18">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2812.71186440678</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="18">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2560.1694915254238</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1341.5254237288136</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="18">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="18">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="18">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="18">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="18">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="18">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="18">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="18">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="18">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="18">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="18">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="18">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="18">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="18">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="18">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="18">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="18">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="18">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="18">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="18">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="18">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" s="18">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="18">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="18">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="18">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="18">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="18">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="18">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="18">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="18">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="18">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" s="18">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="18">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="18">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="18">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53" s="18">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" s="18">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="18">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C56" s="18">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" s="18">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" s="18">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>